--- a/reconcile/test_geonames.xlsx
+++ b/reconcile/test_geonames.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,34 +547,22 @@
           <t>NV</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Nye</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>023</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Henderson</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>36.0397</t>
+          <t>39.25021</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-114.98194</t>
+          <t>-116.75119</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -657,38 +645,638 @@
           <t>ENG</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Worcestershire</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Quatt Malvern</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>00GG147</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>52.49351</t>
+          <t>52.11161</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-2.36268</t>
+          <t>-2.32515</t>
         </is>
       </c>
       <c r="P4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
         <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>haikou</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hainan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>20.03421</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>110.34651</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>detroit</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>42.33143</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>-83.04575</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>silicon valley</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>37.77493</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-122.41942</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>south africa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>shengyang</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sichuan</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>30.4</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>104.528</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>britain</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>sunderland</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>54.90465</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-1.38222</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>belgium</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>brussels</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Brussels Capital</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BRU</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>50.85045</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4.34878</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>thailand</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>hungary</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>budapest</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>47.49835</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>19.04045</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>poland</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>wroclaw</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Lower Silesia</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>17.03333</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>shenzhen</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Guangdong</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>22.54554</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>114.0683</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/reconcile/test_geonames.xlsx
+++ b/reconcile/test_geonames.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,47 +461,32 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>adm_1</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>adm_1_code</t>
+          <t>adm1</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>adm_2</t>
+          <t>adm2</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>adm_2_code</t>
+          <t>adm3</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>adm_3</t>
+          <t>adm4</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>adm_3_code</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>lat</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>lon</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>adm_max_level</t>
+          <t>bbox</t>
         </is>
       </c>
     </row>
@@ -544,25 +529,16 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>39.25021</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-116.75119</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>{'east': -114.039461, 'south': 35.001857, 'north': 42.001842, 'west': -120.006473, 'accuracyLevel': 10}</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -599,9 +575,6 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -637,30 +610,33 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>Malvern</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>52.11161</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-2.32515</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Worcestershire</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Malvern Hills District</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Malvern</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>{'east': -2.3096487882026837, 'south': 52.098513150558674, 'north': 52.11650044806153, 'west': -2.338941299687936, 'accuracyLevel': 1}</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -697,30 +673,25 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Haikou</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Hainan</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Haikou Shi</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>20.03421</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>110.34651</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>{'east': 110.58103655473829, 'south': 19.814182151785108, 'north': 20.25422806821489, 'west': 110.1119873452617, 'accuracyLevel': 2}</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -757,30 +728,29 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Michigan</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Wayne</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>City of Detroit</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>42.33143</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>-83.04575</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>{'east': -82.910451, 'south': 42.255192, 'north': 42.45023, 'west': -83.287803, 'accuracyLevel': 10}</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -815,33 +785,12 @@
           <t>silicon valley</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>37.77493</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-122.41942</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -877,9 +826,6 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -915,30 +861,25 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Shengyang</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Sichuan</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ziyang Shi</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>104.528</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>{'east': 104.53842821442068, 'south': 30.39100635124857, 'north': 30.408993648751427, 'west': 104.51757178557934, 'accuracyLevel': 1}</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -975,30 +916,25 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>54.90465</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-1.38222</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1035,30 +971,29 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>Brussels</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Brussels Capital</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>BRU</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Bruxelles-Capitale</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Arrondissement Brussel-Hoofdstad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>50.85045</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>4.34878</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1095,9 +1030,6 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1138,25 +1070,16 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>Budapest</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>47.49835</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>19.04045</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>{'east': 19.294730808064532, 'south': 47.32711602928824, 'north': 47.66958397071176, 'west': 18.786169191935468, 'accuracyLevel': 2}</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1193,30 +1116,29 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>Wroclaw</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>Lower Silesia</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Wrocław</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Wrocław</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>17.03333</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>{'east': 17.19840487079657, 'south': 50.99657303935859, 'north': 51.203426960641416, 'west': 16.86826112920343, 'accuracyLevel': 2}</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1253,30 +1175,6657 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Guangdong</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>22.54554</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>114.0683</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>{'east': 114.65851861272466, 'south': 22.002593837482305, 'north': 23.088481490481495, 'west': 113.47807806696335, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>pontiac</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pontiac</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Oakland</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>City of Pontiac</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>{'east': -83.247896, 'south': 42.603839, 'north': 42.699623, 'west': -83.335033, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>wuhan</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Wuhan</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Hubei</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Wuhan Shi</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>{'east': 114.75487764069509, 'south': 30.16486277633596, 'north': 31.00180382366404, 'west': 113.77845575930492, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>saxony</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>lancaster</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>City of Lancaster</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>{'east': -76.254038, 'south': 40.006751, 'north': 40.072939, 'west': -76.345902, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ontario</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>{'east': -74.3440298799999, 'south': 41.6814354250001, 'north': 56.859036233, 'west': -95.1548259419999, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>sunnyvale</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>{'east': -121.98242, 'south': 37.329895, 'north': 37.464087, 'west': -122.065265, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>north las vegas</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>North Las Vegas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>{'east': -114.896725, 'south': 36.184833999999995, 'north': 36.436112, 'west': -115.212211, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>south korea</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Korea, Republic of</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>gwangju</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>{'east': 127.10968882167228, 'south': 34.99630863576216, 'north': 35.31313536423784, 'west': 126.72142317832771, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>south africa</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>turkey</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>japan</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>fukuoka</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Fukuoka</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Fukuoka</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Fukuoka City</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Hakata</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>{'east': 130.61489843333152, 'south': 33.43520503717391, 'north': 33.764794962826095, 'west': 130.21843556666846, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="b">
         <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>hungary</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>hatvan</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Hatvan</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Heves County</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>{'east': 19.71005168074891, 'south': 47.64867970249714, 'north': 47.68465429750285, 'west': 19.65661431925109, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>wales</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>neckarsulm</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Neckarsulm</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Baden-Wurttemberg</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Regierungsbezirk Stuttgart</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Landkreis Heilbronn</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Neckarsulm</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>{'east': 9.24973504832279, 'south': 49.175654378278935, 'north': 49.20798465845837, 'west': 9.217042111389558, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>bad rodach</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bad Rodach</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Bavaria</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Upper Franconia</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Landkreis Coburg</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Bad Rodach</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>{'east': 10.86480749094744, 'south': 50.27305975964605, 'north': 50.39269395999577, 'west': 10.712357266796493, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>fremont</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Fremont</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>{'east': -121.86778399999999, 'south': 37.454186, 'north': 37.604624, 'west': -122.149175, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>detroit</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Wayne</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>City of Detroit</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>{'east': -82.910451, 'south': 42.255192, 'north': 42.45023, 'west': -83.287803, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>dresden</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Kreisfreie Stadt Dresden</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>leipzig</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Kreisfreie Stadt Leipzig</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Leipzig</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>{'east': 12.411756004510003, 'south': 51.31210421575785, 'north': 51.35997944123762, 'west': 12.347875462041682, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>united kingdom</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>deeside</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Deeside</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Wales</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Flintshire</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Shotton</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>{'east': -3.0001074529277343, 'south': 53.177602214563535, 'north': 53.223461005045465, 'west': -3.0767052912128907, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>münster</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Münster</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Regierungsbezirk Münster</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Münster</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Münster</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>{'east': 7.671209105910431, 'south': 51.91537136540322, 'north': 51.98867213131061, 'west': 7.5839371596321765, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>united kingdom</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>warwick</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Warwickshire</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Warwick District</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>{'east': -1.5339516254692291, 'south': 52.25754732268303, 'north': 52.30083834824744, 'west': -1.617325525037683, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>netherlands</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>delft</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Delft</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>South Holland</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Delft Municipality</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>{'east': 4.420543578748688, 'south': 51.966698350688134, 'north': 52.04663564931187, 'west': 4.2905684212513115, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>denmark</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>wales</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>st. athan</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>St Athan</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Wales</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Vale of Glamorgan</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>St. Athan</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>{'east': -3.4042087997440293, 'south': 51.39618995888305, 'north': 51.40808284994946, 'west': -3.4256900437463345, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>wuhu</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Wuhu</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Anhui</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Wuhu Shi</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>{'east': 118.621914955991, 'south': 31.188532928773974, 'north': 31.516647071226025, 'west': 118.23702504400899, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F46" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>fremont</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Fremont</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>{'east': -121.86778399999999, 'south': 37.454186, 'north': 37.604624, 'west': -122.149175, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>hamburg</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Hamburg, Freie und Hansestadt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>lünen</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Lünen</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Regierungsbezirk Arnsberg</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Kreis Unna</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Lünen</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>{'east': 7.546356626819443, 'south': 51.59648237051157, 'north': 51.630536149012535, 'west': 7.491793209734007, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>united kingdom</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>malmesbury</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Malmesbury</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Wiltshire</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Malmesbury</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>{'east': -2.080765083488542, 'south': 51.57485068672849, 'north': 51.598893946639095, 'west': -2.116147257743727, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>hangzhou</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Hangzhou</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Zhejiang</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Hangzhou Shi</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>{'east': 120.62015336226078, 'south': 29.899157767921317, 'north': 30.688142232078683, 'west': 119.70268463773921, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ruili</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Ruili</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Zhejiang</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Wenzhou Shi</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>{'east': 120.95477512827279, 'south': 28.42331835124857, 'north': 28.441305648751428, 'west': 120.93431887172721, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>fremont</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Fremont</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>{'east': -121.86778399999999, 'south': 37.454186, 'north': 37.604624, 'west': -122.149175, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F57" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F58" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>beijing</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>{'east': 117.14026891069939, 'south': 39.34225568217476, 'north': 40.47273980070624, 'west': 115.6541875712346, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F59" t="b">
+        <v>0</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>brandenburg</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>{'east': 14.7657018009971, 'south': 51.3590203506627, 'north': 53.5587015183653, 'west': 11.2657319207012, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F60" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>salzgitter</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Salzgitter</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Lower Saxony</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Kreisfreie Stadt Salzgitter</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Salzgitter</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F61" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>emden</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Emden</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Lower Saxony</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Kreisfreie Stadt Emden</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Emden</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>{'east': 7.24054018331388, 'south': 53.333469404564674, 'north': 53.39082510126331, 'west': 7.141750044104904, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="b">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>poland</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="F63" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F64" t="b">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F65" t="b">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>karlstein-großwelzheim</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F66" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>qingdao</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Qingdao</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Shandong</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Qingdao Shi</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>{'east': 120.81241533310391, 'south': 35.717225740831, 'north': 36.41253425916901, 'west': 119.94842466689609, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F68" t="b">
+        <v>0</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>tianjin</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Tianjin</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Tianjin</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Tianjin Municipality</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>{'east': 117.73748930955027, 'south': 38.709941932454704, 'north': 39.574502467545294, 'west': 116.61584409044973, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F69" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>fremont</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Fremont</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>{'east': -121.86778399999999, 'south': 37.454186, 'north': 37.604624, 'west': -122.149175, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>bulgaria</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="F70" t="b">
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>bulgaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>{'east': 28.607429551000003, 'south': 41.235341500000004, 'north': 44.2154806, 'west': 22.357156800000002, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F71" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>aachen</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Cologne District</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Städteregion Aachen</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Aachen</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>{'east': 6.1438548677283755, 'south': 50.73892691283202, 'north': 50.80078678989726, 'west': 6.047295847418284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F72" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>zhejiang</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Zhejiang</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Zhejiang</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>{'east': 122.42025756835938, 'south': 27.17471694946289, 'north': 31.17666244506836, 'west': 117.99832153320312, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F73" t="b">
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>shanghai</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Shanghai Municipality</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>{'east': 122.22039484732596, 'south': 30.574804413735613, 'north': 31.86963998626439, 'west': 120.69571635267403, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F74" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>zuffenhausen</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Zuffenhausen</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Baden-Wurttemberg</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Regierungsbezirk Stuttgart</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Stadtkreis Stuttgart</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>{'east': 9.203430807113508, 'south': 48.82193717197977, 'north': 48.844384701307206, 'west': 9.138011184890955, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>hungary</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="F75" t="b">
+        <v>0</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>komárom</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Komárom</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Komárom-Esztergom</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>{'east': 18.14503799430183, 'south': 47.72576787408204, 'north': 47.76060012591796, 'west': 18.093222005698166, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F76" t="b">
+        <v>0</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>quinghai</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F77" t="b">
+        <v>0</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>shanghai</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Shanghai Municipality</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>{'east': 122.22039484732596, 'south': 30.574804413735613, 'north': 31.86963998626439, 'west': 120.69571635267403, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F78" t="b">
+        <v>0</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>novi</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Novi</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Oakland</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>City of Novi</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>{'east': -83.433672, 'south': 42.435166, 'north': 42.527114, 'west': -83.55521, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F79" t="b">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>california</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="b">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F82" t="b">
+        <v>0</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>vallejo</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Vallejo</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>{'east': -122.16615, 'south': 38.059917999999996, 'north': 38.173496, 'west': -122.38793300000002, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>united kingdom</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F83" t="b">
+        <v>0</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>sunderland</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F84" t="b">
+        <v>0</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>dresden</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Kreisfreie Stadt Dresden</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F85" t="b">
+        <v>0</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>dresden</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Kreisfreie Stadt Dresden</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="F86" t="b">
+        <v>0</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="b">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>hungary</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="F88" t="b">
+        <v>0</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>kecskemét</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kecskemét</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Bács-Kiskun</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>{'east': 19.754115627304806, 'south': 46.863286809608795, 'north': 46.949080750686406, 'west': 19.628437473281195, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F89" t="b">
+        <v>0</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>bollate</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bollate</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Lombardy</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Province of Milan</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Bollate</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>{'east': 9.149364907281392, 'south': 45.53332323644544, 'north': 45.568082918307795, 'west': 9.093122395523253, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="b">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F91" t="b">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>fremont</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Fremont</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>{'east': -121.86778399999999, 'south': 37.454186, 'north': 37.604624, 'west': -122.149175, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="b">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>japan</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="F93" t="b">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>austria</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="F94" t="b">
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>northern austria</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F95" t="b">
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>qinghai</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Qinghai</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Qinghai</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>{'east': 103.04017639160156, 'south': 31.631938934326172, 'north': 39.334716796875, 'west': 89.46499633789062, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>south korea</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Korea, Republic of</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="F96" t="b">
+        <v>0</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>pangyo</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Pangyori</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Gyeonggi-do</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Pyeongtaek-si</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>{'east': 126.96941975773403, 'south': 37.0594353512489, 'north': 37.0774226487511, 'west': 126.94687424226596, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F97" t="b">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>hamburg</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Hamburg, Freie und Hansestadt</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>{'east': 10.32527718680763, 'south': 53.39508508510774, 'north': 53.73943730358849, 'west': 9.730130859481674, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F98" t="b">
+        <v>0</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>silicon valley</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F99" t="b">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>europe</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="b">
+        <v>1</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>morocco</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F101" t="b">
+        <v>0</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>tangier</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Tangier</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Tanger-Tetouan-Al Hoceima</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Tanger-Assilah</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Tanger-Medina</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>{'east': -5.636766009144473, 'south': 35.635242504095686, 'north': 35.8992945610822, 'west': -5.962736554332089, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F102" t="b">
+        <v>0</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>poland</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="F103" t="b">
+        <v>0</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F104" t="b">
+        <v>0</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>costa mesa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Costa Mesa</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>{'east': -117.86427, 'south': 33.625171, 'north': 33.70195, 'west': -117.954085, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F105" t="b">
+        <v>0</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>suzhou</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Suzhou</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Jiangsu</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Suzhou Shi</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>{'east': 120.99050387581104, 'south': 30.967685681307323, 'north': 31.640468318692676, 'west': 120.20025612418897, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>thailand</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="F106" t="b">
+        <v>0</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F107" t="b">
+        <v>0</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>tianjin</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Tianjin</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Tianjin</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Tianjin Municipality</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>{'east': 117.73748930955027, 'south': 38.709941932454704, 'north': 39.574502467545294, 'west': 116.61584409044973, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F108" t="b">
+        <v>0</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>kamenz</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kamenz</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Landkreis Bautzen</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Kamenz</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>{'east': 14.133282026741975, 'south': 51.25923519306523, 'north': 51.29309244289519, 'west': 14.077890184433112, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="F109" t="b">
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>fessenheim</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Fessenheim</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Grand Est</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Haut-Rhin</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Colmar-Ribeauvillé</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Fessenheim</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>{'east': 7.541703019256914, 'south': 47.91115217562429, 'north': 47.920145824375716, 'west': 7.528282980743086, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="F110" t="b">
+        <v>0</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F111" t="b">
+        <v>0</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>coventry</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>{'east': -1.396893966636398, 'south': 52.35188904002982, 'north': 52.459692728796995, 'west': -1.605619370574852, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>united kingdom</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F112" t="b">
+        <v>0</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>sunderland</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F113" t="b">
+        <v>0</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F114" t="b">
+        <v>0</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>las vegas</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>{'east': -115.062164, 'south': 36.129554, 'north': 36.380894999999995, 'west': -115.40657500000002, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F115" t="b">
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>dresden</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Saxony</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Kreisfreie Stadt Dresden</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Dresden</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>{'east': 13.786581145811093, 'south': 51.027883739261306, 'north': 51.07425076373171, 'west': 13.688065285884342, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="F116" t="b">
+        <v>0</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F117" t="b">
+        <v>0</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>beijing</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>{'east': 117.14026891069939, 'south': 39.34225568217476, 'north': 40.47273980070624, 'west': 115.6541875712346, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F118" t="b">
+        <v>0</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>taiyuan</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Taiyuan</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Shanxi</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Taiyuan Shi</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>{'east': 112.90265320264672, 'south': 37.60016007801835, 'north': 38.13872872198165, 'west': 112.21790239735327, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F119" t="b">
+        <v>0</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>suzhou</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Suzhou</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Jiangsu</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Suzhou Shi</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>{'east': 120.99050387581104, 'south': 30.967685681307323, 'north': 31.640468318692676, 'west': 120.20025612418897, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F120" t="b">
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>stuttgart-zuffenhausen</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F121" t="b">
+        <v>0</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>hangzhou</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Hangzhou</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Zhejiang</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Hangzhou Shi</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>{'east': 120.62015336226078, 'south': 29.899157767921317, 'north': 30.688142232078683, 'west': 119.70268463773921, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F122" t="b">
+        <v>0</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>soliera</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Soliera</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Province of Modena</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Soliera</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>{'east': 10.939471639817983, 'south': 44.72078134087546, 'north': 44.744421240369206, 'west': 10.908286143167064, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F123" t="b">
+        <v>0</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>fremont</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Fremont</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>{'east': -121.86778399999999, 'south': 37.454186, 'north': 37.604624, 'west': -122.149175, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="b">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F125" t="b">
+        <v>0</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>orion</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Orion</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Western Township</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>{'east': -90.358491, 'south': 41.340702, 'north': 41.359919, 'west': -90.391474, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="b">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>russia</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="F127" t="b">
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>tashkala</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Tashkala</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Chechnya</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>{'east': 45.641485628204535, 'south': 43.33604954049943, 'north': 43.34324445950057, 'west': 45.63159237179546, 'accuracyLevel': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>thailand</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="F128" t="b">
+        <v>0</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F129" t="b">
+        <v>0</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F130" t="b">
+        <v>0</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>jiangmen</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Jiangmen</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Guangdong</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Jiangmen Shi</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>{'east': 113.27194526644384, 'south': 22.409404410855764, 'north': 22.757262189144235, 'west': 112.89472133355618, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>south korea</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Korea, Republic of</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="F131" t="b">
+        <v>0</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>cheonan</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Cheonan</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Chungcheongnam-do</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Cheonan-si</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>{'east': 127.28397738588262, 'south': 36.70113603663092, 'north': 36.91186396336908, 'west': 127.02042261411736, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F132" t="b">
+        <v>0</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F133" t="b">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>las vegas</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>{'east': -115.062164, 'south': 36.129554, 'north': 36.380894999999995, 'west': -115.40657500000002, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F134" t="b">
+        <v>0</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>xinjiang</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Xinjiang</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Xinjiang</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>{'east': 96.39846801757812, 'south': 34.350013732910156, 'north': 49.17332458496094, 'west': 73.61720275878906, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>britain</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F135" t="b">
+        <v>0</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>sunderland</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>{'east': -1.351172911278187, 'south': 54.85601261436129, 'north': 54.939914387340465, 'west': -1.480882124121284, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="F136" t="b">
+        <v>0</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>flins</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="b">
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="b">
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>belgium</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="F139" t="b">
+        <v>0</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>brussel</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Brussels</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Brussels Capital</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Bruxelles-Capitale</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Arrondissement Brussel-Hoofdstad</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>hungary</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="F140" t="b">
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="F141" t="b">
+        <v>0</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>south africa</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="F142" t="b">
+        <v>0</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>east london</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>East London</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Eastern Cape</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Buffalo City Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Buffalo City</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>{'east': 28.018503381239466, 'south': -33.10499645800343, 'north': -32.92557372892517, 'west': 27.804746435655137, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F143" t="b">
+        <v>0</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>port of la</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="F144" t="b">
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>mexico</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="F145" t="b">
+        <v>0</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>belgium</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="F146" t="b">
+        <v>0</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>brussels</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Brussels</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Brussels Capital</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Bruxelles-Capitale</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Arrondissement Brussel-Hoofdstad</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>{'east': 4.437065865926462, 'south': 50.79634445603754, 'north': 50.91390245974863, 'west': 4.3137684747642435, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>canada</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F147" t="b">
+        <v>0</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>windsor</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Windsor</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Essex County</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>{'east': -82.66831571399996, 'south': 42.208049138000035, 'north': 42.349148541000034, 'west': -83.11042678499997, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F148" t="b">
+        <v>0</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>salzgitter</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Salzgitter</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Lower Saxony</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Kreisfreie Stadt Salzgitter</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Salzgitter</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>{'east': 10.45533584814119, 'south': 52.12864174128801, 'north': 52.19638022714064, 'west': 10.371113225395026, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="b">
+        <v>1</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="F150" t="b">
+        <v>0</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>paterna</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Paterna</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Paterna</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>{'east': -0.39834183163152426, 'south': 39.46989262439202, 'north': 39.53536737560799, 'west': -0.4832381683684758, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F151" t="b">
+        <v>0</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>nanjing</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Nanjing</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Jiangsu</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Nanjing</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>{'east': 119.24730437841608, 'south': 31.66548651938116, 'north': 32.457846880618845, 'west': 118.30825122158392, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="F152" t="b">
+        <v>0</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>suzhou</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Suzhou</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Jiangsu</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Suzhou Shi</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>{'east': 120.99050387581104, 'south': 30.967685681307323, 'north': 31.640468318692676, 'west': 120.20025612418897, 'accuracyLevel': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>united states</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F153" t="b">
+        <v>0</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>fremont</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Fremont</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>{'east': -121.86778399999999, 'south': 37.454186, 'north': 37.604624, 'west': -122.149175, 'accuracyLevel': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="b">
+        <v>1</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>factory</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F155" t="b">
+        <v>0</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>berlin</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>State of Berlin</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Berlin, Stadt</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>{'east': 13.7604692835498, 'south': 52.3382418348765, 'north': 52.6749171487584, 'west': 13.0883332178678, 'accuracyLevel': 10}</t>
+        </is>
       </c>
     </row>
   </sheetData>
